--- a/STEAMEE_KPI_Change_Log_v3.xlsx
+++ b/STEAMEE_KPI_Change_Log_v3.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" tabRatio="600" firstSheet="3" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SUMMARY" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="KPI MASTER LIST" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BUGS &amp; DATA GAPS" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="CLIENT HANDOFF" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="LEGEND" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="NEW APIS REQUIRED" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUMMARY" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI MASTER LIST" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BUGS &amp; DATA GAPS" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CLIENT HANDOFF" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LEGEND" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NEW APIS REQUIRED" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
